--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\njoud\OneDrive\Desktop\Blackboard  ultr\الأدلة\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CF19BA7-779E-45F4-83FC-5E8213035B1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20B97897-CF0E-4F27-9108-8D8B9F1F77F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" xr2:uid="{98144A03-7E5A-4E28-9561-C67424E63F67}"/>
+    <workbookView xWindow="12683" yWindow="4208" windowWidth="9090" windowHeight="10800" xr2:uid="{98144A03-7E5A-4E28-9561-C67424E63F67}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="29">
   <si>
     <t>نوع الدليل</t>
   </si>
@@ -105,6 +105,24 @@
   </si>
   <si>
     <t>https://lifebox.pnu.edu.sa/webconsole/gtl.do?gid=B4W2g7qpuL6Br</t>
+  </si>
+  <si>
+    <t>إرسال رسالة عبر أداة رسائل المقرر</t>
+  </si>
+  <si>
+    <t>التعامل مع لوحة المناقشة</t>
+  </si>
+  <si>
+    <t>إرسال الواجب</t>
+  </si>
+  <si>
+    <t>https://lifebox.pnu.edu.sa/webconsole/gtl.do?gid=rSGdd1dWC</t>
+  </si>
+  <si>
+    <t>https://lifebox.pnu.edu.sa/webconsole/gtl.do?gid=x4cNvSaUK1L</t>
+  </si>
+  <si>
+    <t>https://lifebox.pnu.edu.sa/webconsole/gtl.do?gid=gIaGVI1T</t>
   </si>
 </sst>
 </file>
@@ -149,7 +167,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -172,6 +190,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -507,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8645F845-3E2C-4AF0-BEB9-0DEBCF9E87EF}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.796875" customWidth="1"/>
@@ -647,6 +666,39 @@
         <v>18</v>
       </c>
     </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D4" r:id="rId1" xr:uid="{6EFA2800-8409-44D6-8D0A-9EA75D933CE3}"/>
@@ -658,6 +710,9 @@
     <hyperlink ref="D3" r:id="rId7" xr:uid="{A59AB85F-6CB8-4813-8A2A-01DE18999D04}"/>
     <hyperlink ref="D8" r:id="rId8" xr:uid="{2C681117-2750-43E4-AF2E-78BC20708E6C}"/>
     <hyperlink ref="D9" r:id="rId9" xr:uid="{37D85458-0151-4B73-AD87-DC470916A01F}"/>
+    <hyperlink ref="D11" r:id="rId10" xr:uid="{3D9A41BE-C876-4F44-BD35-126981D7BCA7}"/>
+    <hyperlink ref="D12" r:id="rId11" xr:uid="{FC8E0EBC-1705-488B-AF2F-73CBD3C980C1}"/>
+    <hyperlink ref="D13" r:id="rId12" xr:uid="{C1239A9A-046E-47CC-BC3C-A7A4B184AADE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\njoud\OneDrive\Desktop\Blackboard  ultr\الأدلة\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20B97897-CF0E-4F27-9108-8D8B9F1F77F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F76694-96D3-4D9F-BD95-699FEF6239FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12683" yWindow="4208" windowWidth="9090" windowHeight="10800" xr2:uid="{98144A03-7E5A-4E28-9561-C67424E63F67}"/>
+    <workbookView xWindow="9068" yWindow="1312" windowWidth="9090" windowHeight="10800" xr2:uid="{98144A03-7E5A-4E28-9561-C67424E63F67}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -59,15 +59,6 @@
     <t>تغيير لغة النظام</t>
   </si>
   <si>
-    <t>إنشاء عنصر</t>
-  </si>
-  <si>
-    <t>إنشاء محتوى المقرر الدراسي</t>
-  </si>
-  <si>
-    <t>إنشاء اعلان</t>
-  </si>
-  <si>
     <t>لوحة المناقشة</t>
   </si>
   <si>
@@ -123,6 +114,15 @@
   </si>
   <si>
     <t>https://lifebox.pnu.edu.sa/webconsole/gtl.do?gid=gIaGVI1T</t>
+  </si>
+  <si>
+    <t>إنشاء مستند</t>
+  </si>
+  <si>
+    <t>تنظيم محتوى المقرر الدراسي</t>
+  </si>
+  <si>
+    <t>إنشاء إعلان</t>
   </si>
 </sst>
 </file>
@@ -558,10 +558,10 @@
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E2" s="1"/>
     </row>
@@ -574,7 +574,7 @@
         <v>6</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E3" s="1"/>
     </row>
@@ -584,10 +584,10 @@
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E4" s="1"/>
     </row>
@@ -597,10 +597,10 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E5" s="1"/>
     </row>
@@ -610,10 +610,10 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E6" s="1"/>
     </row>
@@ -623,80 +623,80 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>23</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>24</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>25</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\njoud\OneDrive\Desktop\Blackboard  ultr\الأدلة\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F76694-96D3-4D9F-BD95-699FEF6239FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E86D73-86F1-41CC-8D13-DE00FE48D50A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9068" yWindow="1312" windowWidth="9090" windowHeight="10800" xr2:uid="{98144A03-7E5A-4E28-9561-C67424E63F67}"/>
+    <workbookView xWindow="10395" yWindow="3180" windowWidth="9090" windowHeight="10800" xr2:uid="{98144A03-7E5A-4E28-9561-C67424E63F67}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="35">
   <si>
     <t>نوع الدليل</t>
   </si>
@@ -123,6 +123,24 @@
   </si>
   <si>
     <t>إنشاء إعلان</t>
+  </si>
+  <si>
+    <t>ضبط شروط النشر</t>
+  </si>
+  <si>
+    <t>التعامل مع الواجبات</t>
+  </si>
+  <si>
+    <t>التعامل مع الاختبارات الإلكترونية</t>
+  </si>
+  <si>
+    <t>https://lifebox.pnu.edu.sa/webconsole/gtl.do?gid=TiaD8TT2</t>
+  </si>
+  <si>
+    <t>https://lifebox.pnu.edu.sa/webconsole/gtl.do?gid=oCSDNFW</t>
+  </si>
+  <si>
+    <t>https://lifebox.pnu.edu.sa/webconsole/gtl.do?gid=faqgUmYm</t>
   </si>
 </sst>
 </file>
@@ -526,7 +544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8645F845-3E2C-4AF0-BEB9-0DEBCF9E87EF}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.796875" customWidth="1"/>
@@ -697,6 +715,39 @@
       </c>
       <c r="D13" s="8" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -713,7 +764,11 @@
     <hyperlink ref="D11" r:id="rId10" xr:uid="{3D9A41BE-C876-4F44-BD35-126981D7BCA7}"/>
     <hyperlink ref="D12" r:id="rId11" xr:uid="{FC8E0EBC-1705-488B-AF2F-73CBD3C980C1}"/>
     <hyperlink ref="D13" r:id="rId12" xr:uid="{C1239A9A-046E-47CC-BC3C-A7A4B184AADE}"/>
+    <hyperlink ref="D14" r:id="rId13" xr:uid="{802FB9E8-8F4F-45A2-A33B-AD260D3EFA9B}"/>
+    <hyperlink ref="D15" r:id="rId14" xr:uid="{E23956FD-8F0F-4A78-9875-E527AA8B54D8}"/>
+    <hyperlink ref="D16" r:id="rId15" xr:uid="{C6DDB4E0-72CA-48D6-9AC6-0FF90C0AD52A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId16"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\njoud\OneDrive\Desktop\Blackboard  ultr\الأدلة\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E86D73-86F1-41CC-8D13-DE00FE48D50A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B36559FD-1910-447B-A0F2-237966072A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10395" yWindow="3180" windowWidth="9090" windowHeight="10800" xr2:uid="{98144A03-7E5A-4E28-9561-C67424E63F67}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" xr2:uid="{98144A03-7E5A-4E28-9561-C67424E63F67}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="41">
   <si>
     <t>نوع الدليل</t>
   </si>
@@ -141,6 +141,24 @@
   </si>
   <si>
     <t>https://lifebox.pnu.edu.sa/webconsole/gtl.do?gid=faqgUmYm</t>
+  </si>
+  <si>
+    <t>إنشاء المجموعات</t>
+  </si>
+  <si>
+    <t>انشاء قواعد التقدير rubric</t>
+  </si>
+  <si>
+    <t>التعامل مع بنوك الأسئلة</t>
+  </si>
+  <si>
+    <t>https://lifebox.pnu.edu.sa/webconsole/gtl.do?gid=pPasBpM</t>
+  </si>
+  <si>
+    <t>https://lifebox.pnu.edu.sa/webconsole/gtl.do?gid=7G8id4iVDLYGm</t>
+  </si>
+  <si>
+    <t>https://lifebox.pnu.edu.sa/webconsole/gtl.do?gid=ptvGTubq6kNcR</t>
   </si>
 </sst>
 </file>
@@ -544,7 +562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8645F845-3E2C-4AF0-BEB9-0DEBCF9E87EF}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.796875" customWidth="1"/>
@@ -748,6 +766,39 @@
       </c>
       <c r="D16" s="8" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A17" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A18" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A19" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -767,8 +818,11 @@
     <hyperlink ref="D14" r:id="rId13" xr:uid="{802FB9E8-8F4F-45A2-A33B-AD260D3EFA9B}"/>
     <hyperlink ref="D15" r:id="rId14" xr:uid="{E23956FD-8F0F-4A78-9875-E527AA8B54D8}"/>
     <hyperlink ref="D16" r:id="rId15" xr:uid="{C6DDB4E0-72CA-48D6-9AC6-0FF90C0AD52A}"/>
+    <hyperlink ref="D17" r:id="rId16" xr:uid="{7EBAD696-1A49-4EC8-B89A-AC41EB62FC3B}"/>
+    <hyperlink ref="D18" r:id="rId17" xr:uid="{891B0597-E966-4684-8DC5-34B931B188D6}"/>
+    <hyperlink ref="D19" r:id="rId18" xr:uid="{94DCFF04-F563-4EC3-B994-5C52DBC61257}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId16"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId19"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\njoud\OneDrive\Desktop\Blackboard  ultr\الأدلة\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B36559FD-1910-447B-A0F2-237966072A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{207C307F-898A-4BBB-BD67-2A0D373CF0A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" xr2:uid="{98144A03-7E5A-4E28-9561-C67424E63F67}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="39">
   <si>
     <t>نوع الدليل</t>
   </si>
@@ -131,16 +131,10 @@
     <t>التعامل مع الواجبات</t>
   </si>
   <si>
-    <t>التعامل مع الاختبارات الإلكترونية</t>
-  </si>
-  <si>
     <t>https://lifebox.pnu.edu.sa/webconsole/gtl.do?gid=TiaD8TT2</t>
   </si>
   <si>
     <t>https://lifebox.pnu.edu.sa/webconsole/gtl.do?gid=oCSDNFW</t>
-  </si>
-  <si>
-    <t>https://lifebox.pnu.edu.sa/webconsole/gtl.do?gid=faqgUmYm</t>
   </si>
   <si>
     <t>إنشاء المجموعات</t>
@@ -562,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8645F845-3E2C-4AF0-BEB9-0DEBCF9E87EF}">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.796875" customWidth="1"/>
@@ -743,7 +737,7 @@
         <v>29</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
@@ -754,18 +748,18 @@
         <v>30</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>31</v>
+      <c r="C16" t="s">
+        <v>33</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
@@ -773,10 +767,10 @@
         <v>5</v>
       </c>
       <c r="C17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.45">
@@ -784,21 +778,10 @@
         <v>5</v>
       </c>
       <c r="C18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A19" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C19" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -817,12 +800,11 @@
     <hyperlink ref="D13" r:id="rId12" xr:uid="{C1239A9A-046E-47CC-BC3C-A7A4B184AADE}"/>
     <hyperlink ref="D14" r:id="rId13" xr:uid="{802FB9E8-8F4F-45A2-A33B-AD260D3EFA9B}"/>
     <hyperlink ref="D15" r:id="rId14" xr:uid="{E23956FD-8F0F-4A78-9875-E527AA8B54D8}"/>
-    <hyperlink ref="D16" r:id="rId15" xr:uid="{C6DDB4E0-72CA-48D6-9AC6-0FF90C0AD52A}"/>
-    <hyperlink ref="D17" r:id="rId16" xr:uid="{7EBAD696-1A49-4EC8-B89A-AC41EB62FC3B}"/>
-    <hyperlink ref="D18" r:id="rId17" xr:uid="{891B0597-E966-4684-8DC5-34B931B188D6}"/>
-    <hyperlink ref="D19" r:id="rId18" xr:uid="{94DCFF04-F563-4EC3-B994-5C52DBC61257}"/>
+    <hyperlink ref="D16" r:id="rId15" xr:uid="{7EBAD696-1A49-4EC8-B89A-AC41EB62FC3B}"/>
+    <hyperlink ref="D17" r:id="rId16" xr:uid="{891B0597-E966-4684-8DC5-34B931B188D6}"/>
+    <hyperlink ref="D18" r:id="rId17" xr:uid="{94DCFF04-F563-4EC3-B994-5C52DBC61257}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId19"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId18"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\njoud\OneDrive\Desktop\Blackboard  ultr\الأدلة\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{207C307F-898A-4BBB-BD67-2A0D373CF0A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3471ADB-FC5C-4B94-8FAC-7139D17C3589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" xr2:uid="{98144A03-7E5A-4E28-9561-C67424E63F67}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="49">
   <si>
     <t>نوع الدليل</t>
   </si>
@@ -153,6 +153,36 @@
   </si>
   <si>
     <t>https://lifebox.pnu.edu.sa/webconsole/gtl.do?gid=ptvGTubq6kNcR</t>
+  </si>
+  <si>
+    <t>الفصول الافتراضية</t>
+  </si>
+  <si>
+    <t>https://lifebox.pnu.edu.sa/webconsole/gtl.do?gid=BwnVdC</t>
+  </si>
+  <si>
+    <t>التعامل مع الاختبارات الإلكترونية</t>
+  </si>
+  <si>
+    <t>التعامل مع دفتر التقديرات</t>
+  </si>
+  <si>
+    <t>https://lifebox.pnu.edu.sa/webconsole/gtl.do?gid=faqgUmYm</t>
+  </si>
+  <si>
+    <t>https://lifebox.pnu.edu.sa/webconsole/gtl.do?gid=awtyxPbzDe</t>
+  </si>
+  <si>
+    <t>تقديم اختبار</t>
+  </si>
+  <si>
+    <t>استعراض الدرجات والملاحظات</t>
+  </si>
+  <si>
+    <t>https://lifebox.pnu.edu.sa/webconsole/gtl.do?gid=Hw8CEB</t>
+  </si>
+  <si>
+    <t>https://lifebox.pnu.edu.sa/webconsole/gtl.do?gid=YV6zh4bw</t>
   </si>
 </sst>
 </file>
@@ -205,15 +235,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -221,6 +242,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -556,23 +586,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8645F845-3E2C-4AF0-BEB9-0DEBCF9E87EF}">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="16.796875" customWidth="1"/>
-    <col min="3" max="3" width="31.1328125" customWidth="1"/>
+    <col min="1" max="1" width="16.796875" style="7" customWidth="1"/>
+    <col min="2" max="2" width="9.06640625" style="7"/>
+    <col min="3" max="3" width="31.1328125" style="7" customWidth="1"/>
     <col min="4" max="4" width="54.06640625" customWidth="1"/>
     <col min="5" max="5" width="38.265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -583,205 +614,257 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="3" t="s">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2" t="s">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E3" s="1"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2" t="s">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2" t="s">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2" t="s">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="1"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2" t="s">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="5" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A14" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="4" t="s">
+      <c r="A14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A15" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="4" t="s">
+      <c r="A15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="5" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A16" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="A16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="5" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A17" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="A17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="5" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A18" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="A18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="5" t="s">
         <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A22" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A23" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -803,8 +886,13 @@
     <hyperlink ref="D16" r:id="rId15" xr:uid="{7EBAD696-1A49-4EC8-B89A-AC41EB62FC3B}"/>
     <hyperlink ref="D17" r:id="rId16" xr:uid="{891B0597-E966-4684-8DC5-34B931B188D6}"/>
     <hyperlink ref="D18" r:id="rId17" xr:uid="{94DCFF04-F563-4EC3-B994-5C52DBC61257}"/>
+    <hyperlink ref="D19" r:id="rId18" xr:uid="{FA33EECF-7B8E-474E-98AF-065F84635216}"/>
+    <hyperlink ref="D20" r:id="rId19" xr:uid="{4300B880-13E9-49AE-85F0-2319866B48D1}"/>
+    <hyperlink ref="D21" r:id="rId20" xr:uid="{0A1AFCD2-CFA1-4132-AF2E-D8DA029714F5}"/>
+    <hyperlink ref="D22" r:id="rId21" xr:uid="{8FCE4CE0-96F4-44F6-B205-6FA61A0E8F92}"/>
+    <hyperlink ref="D23" r:id="rId22" xr:uid="{EB3AE423-DDE0-4AF5-979F-B4C97C74BD12}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId18"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId23"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\njoud\OneDrive\Desktop\Blackboard  ultr\الأدلة\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3471ADB-FC5C-4B94-8FAC-7139D17C3589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E9053BA-6841-402F-BB17-04D8D1496B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" xr2:uid="{98144A03-7E5A-4E28-9561-C67424E63F67}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="56">
   <si>
     <t>نوع الدليل</t>
   </si>
@@ -183,6 +183,27 @@
   </si>
   <si>
     <t>https://lifebox.pnu.edu.sa/webconsole/gtl.do?gid=YV6zh4bw</t>
+  </si>
+  <si>
+    <t>https://lifebox.pnu.edu.sa/webconsole/gtl.do?gid=MrAK85KCCLpix</t>
+  </si>
+  <si>
+    <t>التعامل مع أداة رسائل المقرر</t>
+  </si>
+  <si>
+    <t>نسخ عناصر المقرر</t>
+  </si>
+  <si>
+    <t>ضبط التنبيهات والاشعارات</t>
+  </si>
+  <si>
+    <t>https://lifebox.pnu.edu.sa/webconsole/gtl.do?gid=xs5uL2HqR9</t>
+  </si>
+  <si>
+    <t>https://lifebox.pnu.edu.sa/webconsole/gtl.do?gid=4yrBYeaSBKNEVZ</t>
+  </si>
+  <si>
+    <t>https://lifebox.pnu.edu.sa/webconsole/gtl.do?gid=ZRecgqOBSPN</t>
   </si>
 </sst>
 </file>
@@ -586,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8645F845-3E2C-4AF0-BEB9-0DEBCF9E87EF}">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.796875" style="7" customWidth="1"/>
@@ -865,6 +886,61 @@
       </c>
       <c r="D23" s="5" t="s">
         <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A24" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A25" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A26" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A27" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A28" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -891,8 +967,13 @@
     <hyperlink ref="D21" r:id="rId20" xr:uid="{0A1AFCD2-CFA1-4132-AF2E-D8DA029714F5}"/>
     <hyperlink ref="D22" r:id="rId21" xr:uid="{8FCE4CE0-96F4-44F6-B205-6FA61A0E8F92}"/>
     <hyperlink ref="D23" r:id="rId22" xr:uid="{EB3AE423-DDE0-4AF5-979F-B4C97C74BD12}"/>
+    <hyperlink ref="D24" r:id="rId23" xr:uid="{0E1EED8A-3192-46F0-A648-C8BF5DB56A4A}"/>
+    <hyperlink ref="D25" r:id="rId24" xr:uid="{301B7DD1-1C9B-42A9-9A5C-5995ED4BA7B7}"/>
+    <hyperlink ref="D26" r:id="rId25" xr:uid="{0BD95E6B-3CFA-4061-A607-CA4DCE1C1DF2}"/>
+    <hyperlink ref="D27" r:id="rId26" xr:uid="{9B5182DE-0747-4823-A25E-ECA241AAF709}"/>
+    <hyperlink ref="D28" r:id="rId27" xr:uid="{883B02E8-2D7B-44C0-868C-1F5EB380BD95}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId23"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId28"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\njoud\OneDrive\Desktop\Blackboard  ultr\الأدلة\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E9053BA-6841-402F-BB17-04D8D1496B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC5E6C2-18C2-4931-B227-DD5F7543572E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" xr2:uid="{98144A03-7E5A-4E28-9561-C67424E63F67}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="62">
   <si>
     <t>نوع الدليل</t>
   </si>
@@ -140,9 +140,6 @@
     <t>إنشاء المجموعات</t>
   </si>
   <si>
-    <t>انشاء قواعد التقدير rubric</t>
-  </si>
-  <si>
     <t>التعامل مع بنوك الأسئلة</t>
   </si>
   <si>
@@ -204,6 +201,27 @@
   </si>
   <si>
     <t>https://lifebox.pnu.edu.sa/webconsole/gtl.do?gid=ZRecgqOBSPN</t>
+  </si>
+  <si>
+    <t>بدء الاستخدام</t>
+  </si>
+  <si>
+    <t>أدوات التواصل</t>
+  </si>
+  <si>
+    <t>أدوات التفاعل</t>
+  </si>
+  <si>
+    <t>أدوات التقييم</t>
+  </si>
+  <si>
+    <t>الدرجات</t>
+  </si>
+  <si>
+    <t>إدارة المحتوى</t>
+  </si>
+  <si>
+    <t>إنشاء قواعد التقدير rubric</t>
   </si>
 </sst>
 </file>
@@ -607,11 +625,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8645F845-3E2C-4AF0-BEB9-0DEBCF9E87EF}">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.796875" style="7" customWidth="1"/>
-    <col min="2" max="2" width="9.06640625" style="7"/>
+    <col min="2" max="2" width="15.3984375" style="7" customWidth="1"/>
     <col min="3" max="3" width="31.1328125" style="7" customWidth="1"/>
     <col min="4" max="4" width="54.06640625" customWidth="1"/>
     <col min="5" max="5" width="38.265625" customWidth="1"/>
@@ -638,7 +656,9 @@
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1"/>
+      <c r="B2" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="C2" s="6" t="s">
         <v>12</v>
       </c>
@@ -651,7 +671,9 @@
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="1"/>
+      <c r="B3" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
@@ -664,7 +686,9 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="1"/>
+      <c r="B4" s="7" t="s">
+        <v>60</v>
+      </c>
       <c r="C4" s="1" t="s">
         <v>26</v>
       </c>
@@ -677,7 +701,9 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="1"/>
+      <c r="B5" s="7" t="s">
+        <v>60</v>
+      </c>
       <c r="C5" s="1" t="s">
         <v>27</v>
       </c>
@@ -690,7 +716,9 @@
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="1"/>
+      <c r="B6" s="7" t="s">
+        <v>56</v>
+      </c>
       <c r="C6" s="1" t="s">
         <v>28</v>
       </c>
@@ -703,7 +731,9 @@
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="1"/>
+      <c r="B7" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="C7" s="1" t="s">
         <v>7</v>
       </c>
@@ -716,6 +746,9 @@
       <c r="A8" s="7" t="s">
         <v>13</v>
       </c>
+      <c r="B8" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="C8" s="8" t="s">
         <v>12</v>
       </c>
@@ -727,6 +760,9 @@
       <c r="A9" s="7" t="s">
         <v>13</v>
       </c>
+      <c r="B9" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="C9" s="7" t="s">
         <v>6</v>
       </c>
@@ -738,6 +774,9 @@
       <c r="A10" s="7" t="s">
         <v>13</v>
       </c>
+      <c r="B10" s="7" t="s">
+        <v>56</v>
+      </c>
       <c r="C10" s="7" t="s">
         <v>14</v>
       </c>
@@ -749,6 +788,9 @@
       <c r="A11" s="7" t="s">
         <v>13</v>
       </c>
+      <c r="B11" s="7" t="s">
+        <v>56</v>
+      </c>
       <c r="C11" s="7" t="s">
         <v>20</v>
       </c>
@@ -760,6 +802,9 @@
       <c r="A12" s="7" t="s">
         <v>13</v>
       </c>
+      <c r="B12" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="C12" s="7" t="s">
         <v>21</v>
       </c>
@@ -771,6 +816,9 @@
       <c r="A13" s="7" t="s">
         <v>13</v>
       </c>
+      <c r="B13" s="7" t="s">
+        <v>58</v>
+      </c>
       <c r="C13" s="7" t="s">
         <v>22</v>
       </c>
@@ -782,6 +830,9 @@
       <c r="A14" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B14" s="7" t="s">
+        <v>60</v>
+      </c>
       <c r="C14" s="7" t="s">
         <v>29</v>
       </c>
@@ -793,6 +844,9 @@
       <c r="A15" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B15" s="7" t="s">
+        <v>58</v>
+      </c>
       <c r="C15" s="7" t="s">
         <v>30</v>
       </c>
@@ -804,105 +858,135 @@
       <c r="A16" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B16" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="C16" s="7" t="s">
         <v>33</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B17" s="7" t="s">
+        <v>58</v>
+      </c>
       <c r="C17" s="7" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B18" s="7" t="s">
+        <v>58</v>
+      </c>
       <c r="C18" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B19" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="C19" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B20" s="7" t="s">
+        <v>58</v>
+      </c>
       <c r="C20" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B21" s="7" t="s">
+        <v>59</v>
+      </c>
       <c r="C21" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" s="7" t="s">
         <v>13</v>
       </c>
+      <c r="B22" s="7" t="s">
+        <v>58</v>
+      </c>
       <c r="C22" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" s="7" t="s">
         <v>13</v>
       </c>
+      <c r="B23" s="7" t="s">
+        <v>59</v>
+      </c>
       <c r="C23" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" s="7" t="s">
         <v>13</v>
       </c>
+      <c r="B24" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="C24" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" s="7" t="s">
         <v>13</v>
       </c>
+      <c r="B25" s="7" t="s">
+        <v>58</v>
+      </c>
       <c r="C25" s="7" t="s">
         <v>22</v>
       </c>
@@ -914,34 +998,49 @@
       <c r="A26" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B26" s="7" t="s">
+        <v>56</v>
+      </c>
       <c r="C26" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B27" s="7" t="s">
+        <v>60</v>
+      </c>
       <c r="C27" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B28" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="C28" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D28" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D28" s="5" t="s">
-        <v>53</v>
-      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A33" s="8"/>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A54" s="8"/>
     </row>
   </sheetData>
   <hyperlinks>
